--- a/bandi_program/주간프로그램 계획표(2026).xlsx
+++ b/bandi_program/주간프로그램 계획표(2026).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jimmychoi/Library/Mobile Documents/com~apple~CloudDocs/bandihr/bandi_program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A1090C-59A3-7E45-AD10-5274B368B4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28DCF4D-6754-C44F-A77C-8E359BD36A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34680" yWindow="3640" windowWidth="28800" windowHeight="17400" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36840" yWindow="2140" windowWidth="28800" windowHeight="17400" firstSheet="5" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4월 1주차" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="8월1주차" sheetId="22" r:id="rId18"/>
     <sheet name="8월 2주차" sheetId="23" r:id="rId19"/>
     <sheet name="8월 3주차" sheetId="25" r:id="rId20"/>
+    <sheet name="8월4주차" sheetId="26" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'4월 1주차'!$A$1:$H$53</definedName>
@@ -55,13 +56,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="18">'8월 2주차'!$A$1:$H$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'8월 3주차'!$A$1:$H$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'8월1주차'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'8월4주차'!$A$1:$H$52</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="881">
   <si>
     <r>
       <rPr>
@@ -23149,6 +23151,998 @@
   <si>
     <r>
       <t>(8월 3주차</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼옛체"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(인지)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>독도는 우리땅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="17"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(믿음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(인지)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>9월 달력 만들기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="17"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(믿음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(인지)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도형색깔 맞추기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="17"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(믿음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(인지)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>절기"처서"알아보기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="17"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(믿음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF181717"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>접시제기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(신체)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(사랑반)</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부채로 탁구공
+릴레이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(신체)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(사랑반)</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(인지)
+세계도시 색칠하기
+-싱가폴-
+(전체)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종이접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(인지)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종이배 접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(소망반)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(인지)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+화폐계산하기
+(전체)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>협력 컵쌓기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(신체)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(소망반)</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <t>(인지)
+절기"처서"알아보기
+(소망,사랑반)
+준비:강선진</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(인지)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+독도는 우리땅
+(소망,사랑반)
+준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(인지)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>9월 달력 만들기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(소망,사랑반)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="4" tint="-0.499984740745262"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(인지)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+도형색깔맞추기
+(소망,사랑반)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종이접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(인지)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종이배 접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(사랑반)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞춤형-소리담
+늴리리 맘보
+(사랑반)
+김소정강사</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞춤형-활기담
+공따라 웃음따라
+(믿음반)
+이현주강사</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>윷놀이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(신체)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(행복반)</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종이접기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(인지)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나는 개똥벌레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(사랑반)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞춤형-인지담
+색깔따라 도형찾기
+(사랑반)
+김소정강사</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞춤형-오감담
+보랏빛 행복송이
+(믿음반)
+고현선강사</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>농구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(신체)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(믿음반)</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">미술활동(인지)
+포도송이 만들기                  (사랑반)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="휴먼모음T"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비:강선진</t>
+    </r>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/29 강당:김은비</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/28 강당:정성진</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/27 강당: 강선진</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/26 강당:정성진</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/25 강당: 강선진</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/24 강당: 김은비</t>
+    <phoneticPr fontId="82" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(8월 4주차</t>
     </r>
     <r>
       <rPr>
@@ -25713,7 +26707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="855">
+  <cellXfs count="856">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -28277,6 +29271,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="35" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -29621,6 +30618,188 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>241732</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>68035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1461993</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="_x304906912" descr="EMB0000310028f8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E691B501-6A2C-AF4E-930D-658DD4AE8BC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2222932" y="10647135"/>
+          <a:ext cx="1740961" cy="527050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>342899</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="_x304906912" descr="EMB0000310028f8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC8740AC-19C3-2842-B148-AE3B8EFE0116}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9118600" y="10685780"/>
+          <a:ext cx="2451099" cy="594360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>617220</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="_x304906912" descr="EMB0000310028f8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4986C03D-8B03-B84A-828F-AE40C0E6B03A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9982200" y="6553200"/>
+          <a:ext cx="3843020" cy="1602740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1685705" cy="1432120"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8F27796-0EBF-4D4C-80C2-9BB8BD85C8FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7264400" y="10795000"/>
+          <a:ext cx="1685705" cy="1432120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -44236,6 +45415,1079 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFB6761-36E7-BB41-A585-182412F261D9}">
+  <dimension ref="A1:P60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" style="98" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="99" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" style="98" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="98" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="98" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="98" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" style="98" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="98" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="98"/>
+    <col min="10" max="10" width="9.6640625" style="98" customWidth="1"/>
+    <col min="11" max="11" width="18.5" style="98" customWidth="1"/>
+    <col min="12" max="12" width="19" style="98" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" style="98" customWidth="1"/>
+    <col min="14" max="16" width="18.5" style="98" customWidth="1"/>
+    <col min="17" max="16384" width="8.6640625" style="98"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30.75" customHeight="1">
+      <c r="A1" s="237" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="146" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="146" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="145" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="48.75" customHeight="1">
+      <c r="A2" s="239"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="144" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" s="143" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="142" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="42.75" customHeight="1" thickBot="1">
+      <c r="A3" s="241"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="243" t="s">
+        <v>880</v>
+      </c>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245"/>
+    </row>
+    <row r="4" spans="1:16" ht="24.75" customHeight="1">
+      <c r="A4" s="246" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="247"/>
+      <c r="C4" s="141" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="140" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="140" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="139" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="138" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="137" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="136" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="N4" s="136" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="136" t="s">
+        <v>81</v>
+      </c>
+      <c r="P4" s="135" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="24.75" customHeight="1">
+      <c r="A5" s="248" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="249"/>
+      <c r="C5" s="134" t="s">
+        <v>879</v>
+      </c>
+      <c r="D5" s="134" t="s">
+        <v>878</v>
+      </c>
+      <c r="E5" s="205" t="s">
+        <v>877</v>
+      </c>
+      <c r="F5" s="134" t="s">
+        <v>876</v>
+      </c>
+      <c r="G5" s="134" t="s">
+        <v>875</v>
+      </c>
+      <c r="H5" s="218" t="s">
+        <v>874</v>
+      </c>
+      <c r="J5" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="K5" s="132" t="s">
+        <v>220</v>
+      </c>
+      <c r="L5" s="132"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="132"/>
+    </row>
+    <row r="6" spans="1:16" ht="24" customHeight="1">
+      <c r="A6" s="250" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="253" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="255"/>
+      <c r="G6" s="255"/>
+      <c r="H6" s="256"/>
+      <c r="J6" s="98" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="132"/>
+      <c r="L6" s="132"/>
+      <c r="M6" s="132"/>
+      <c r="N6" s="132"/>
+      <c r="O6" s="132"/>
+      <c r="P6" s="132"/>
+    </row>
+    <row r="7" spans="1:16" ht="24" customHeight="1">
+      <c r="A7" s="251"/>
+      <c r="B7" s="131" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="257" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="258"/>
+      <c r="E7" s="258"/>
+      <c r="F7" s="258"/>
+      <c r="G7" s="258"/>
+      <c r="H7" s="259"/>
+    </row>
+    <row r="8" spans="1:16" ht="24" customHeight="1">
+      <c r="A8" s="251"/>
+      <c r="B8" s="106" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="260" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="261"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="261"/>
+      <c r="G8" s="261"/>
+      <c r="H8" s="262"/>
+      <c r="K8" s="98" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A9" s="251"/>
+      <c r="B9" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="263" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="265"/>
+      <c r="J9" s="98" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" s="98" t="s">
+        <v>215</v>
+      </c>
+      <c r="L9" s="98" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A10" s="252"/>
+      <c r="B10" s="232" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="569" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="569" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="569" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="569" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" s="569" t="s">
+        <v>213</v>
+      </c>
+      <c r="H10" s="848" t="s">
+        <v>728</v>
+      </c>
+      <c r="K10" s="129"/>
+    </row>
+    <row r="11" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A11" s="252"/>
+      <c r="B11" s="232"/>
+      <c r="C11" s="569"/>
+      <c r="D11" s="569"/>
+      <c r="E11" s="569"/>
+      <c r="F11" s="569"/>
+      <c r="G11" s="569"/>
+      <c r="H11" s="848"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="126"/>
+    </row>
+    <row r="12" spans="1:16" ht="27" customHeight="1">
+      <c r="A12" s="252"/>
+      <c r="B12" s="232"/>
+      <c r="C12" s="272" t="s">
+        <v>873</v>
+      </c>
+      <c r="D12" s="342" t="s">
+        <v>872</v>
+      </c>
+      <c r="E12" s="283" t="s">
+        <v>871</v>
+      </c>
+      <c r="F12" s="796" t="s">
+        <v>870</v>
+      </c>
+      <c r="G12" s="305" t="s">
+        <v>869</v>
+      </c>
+      <c r="H12" s="270" t="s">
+        <v>868</v>
+      </c>
+      <c r="K12" s="289" t="s">
+        <v>198</v>
+      </c>
+      <c r="L12" s="290" t="s">
+        <v>206</v>
+      </c>
+      <c r="M12" s="127"/>
+      <c r="N12" s="576" t="s">
+        <v>205</v>
+      </c>
+      <c r="O12" s="126"/>
+    </row>
+    <row r="13" spans="1:16" ht="27" customHeight="1">
+      <c r="A13" s="252"/>
+      <c r="B13" s="232"/>
+      <c r="C13" s="273"/>
+      <c r="D13" s="343"/>
+      <c r="E13" s="283"/>
+      <c r="F13" s="797"/>
+      <c r="G13" s="306"/>
+      <c r="H13" s="270"/>
+      <c r="K13" s="289"/>
+      <c r="L13" s="291"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="576"/>
+      <c r="O13" s="126"/>
+    </row>
+    <row r="14" spans="1:16" ht="27" customHeight="1">
+      <c r="A14" s="252"/>
+      <c r="B14" s="232"/>
+      <c r="C14" s="273"/>
+      <c r="D14" s="343"/>
+      <c r="E14" s="283"/>
+      <c r="F14" s="797"/>
+      <c r="G14" s="306"/>
+      <c r="H14" s="270"/>
+      <c r="K14" s="289"/>
+      <c r="L14" s="291"/>
+      <c r="N14" s="576"/>
+    </row>
+    <row r="15" spans="1:16" ht="27" customHeight="1">
+      <c r="A15" s="252"/>
+      <c r="B15" s="232"/>
+      <c r="C15" s="274"/>
+      <c r="D15" s="344"/>
+      <c r="E15" s="283"/>
+      <c r="F15" s="798"/>
+      <c r="G15" s="307"/>
+      <c r="H15" s="270"/>
+      <c r="K15" s="289"/>
+      <c r="L15" s="292"/>
+      <c r="N15" s="577"/>
+      <c r="P15" s="125"/>
+    </row>
+    <row r="16" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A16" s="252"/>
+      <c r="B16" s="232"/>
+      <c r="C16" s="283" t="s">
+        <v>867</v>
+      </c>
+      <c r="D16" s="283" t="s">
+        <v>866</v>
+      </c>
+      <c r="E16" s="305" t="s">
+        <v>865</v>
+      </c>
+      <c r="F16" s="342" t="s">
+        <v>755</v>
+      </c>
+      <c r="G16" s="342" t="s">
+        <v>754</v>
+      </c>
+      <c r="H16" s="270"/>
+      <c r="K16" s="266" t="s">
+        <v>199</v>
+      </c>
+      <c r="L16" s="124" t="s">
+        <v>198</v>
+      </c>
+      <c r="M16" s="269" t="s">
+        <v>197</v>
+      </c>
+      <c r="N16" s="272" t="s">
+        <v>162</v>
+      </c>
+      <c r="O16" s="275" t="s">
+        <v>196</v>
+      </c>
+      <c r="P16" s="283" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A17" s="252"/>
+      <c r="B17" s="232"/>
+      <c r="C17" s="283"/>
+      <c r="D17" s="283"/>
+      <c r="E17" s="306"/>
+      <c r="F17" s="343"/>
+      <c r="G17" s="343"/>
+      <c r="H17" s="270"/>
+      <c r="K17" s="267"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="269"/>
+      <c r="N17" s="273"/>
+      <c r="O17" s="276"/>
+      <c r="P17" s="283"/>
+    </row>
+    <row r="18" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A18" s="252"/>
+      <c r="B18" s="232"/>
+      <c r="C18" s="283"/>
+      <c r="D18" s="283"/>
+      <c r="E18" s="306"/>
+      <c r="F18" s="343"/>
+      <c r="G18" s="343"/>
+      <c r="H18" s="270"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="269"/>
+      <c r="N18" s="273"/>
+      <c r="O18" s="276"/>
+      <c r="P18" s="283"/>
+    </row>
+    <row r="19" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A19" s="252"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="283"/>
+      <c r="D19" s="283"/>
+      <c r="E19" s="307"/>
+      <c r="F19" s="344"/>
+      <c r="G19" s="344"/>
+      <c r="H19" s="271"/>
+      <c r="K19" s="268"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="269"/>
+      <c r="N19" s="274"/>
+      <c r="O19" s="277"/>
+      <c r="P19" s="283"/>
+    </row>
+    <row r="20" spans="1:16" ht="21" customHeight="1">
+      <c r="A20" s="299" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="108" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="301" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="301"/>
+      <c r="E20" s="301"/>
+      <c r="F20" s="301"/>
+      <c r="G20" s="301"/>
+      <c r="H20" s="302"/>
+      <c r="K20" s="123"/>
+      <c r="N20" s="120"/>
+    </row>
+    <row r="21" spans="1:16" ht="21" customHeight="1">
+      <c r="A21" s="252"/>
+      <c r="B21" s="108" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="303" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="303"/>
+      <c r="E21" s="303"/>
+      <c r="F21" s="303"/>
+      <c r="G21" s="303"/>
+      <c r="H21" s="304"/>
+      <c r="L21" s="305" t="s">
+        <v>192</v>
+      </c>
+      <c r="M21" s="308" t="s">
+        <v>192</v>
+      </c>
+      <c r="N21" s="120"/>
+    </row>
+    <row r="22" spans="1:16" ht="21" customHeight="1">
+      <c r="A22" s="252"/>
+      <c r="B22" s="122" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="310" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="310"/>
+      <c r="E22" s="310"/>
+      <c r="F22" s="310"/>
+      <c r="G22" s="310"/>
+      <c r="H22" s="311"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="306"/>
+      <c r="M22" s="309"/>
+      <c r="N22" s="120"/>
+    </row>
+    <row r="23" spans="1:16" ht="11.25" customHeight="1">
+      <c r="A23" s="252"/>
+      <c r="B23" s="312" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="233" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="569" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="569" t="s">
+        <v>189</v>
+      </c>
+      <c r="F23" s="569" t="s">
+        <v>189</v>
+      </c>
+      <c r="G23" s="569" t="s">
+        <v>189</v>
+      </c>
+      <c r="H23" s="849" t="s">
+        <v>718</v>
+      </c>
+      <c r="K23" s="121"/>
+      <c r="L23" s="306"/>
+      <c r="M23" s="309"/>
+      <c r="N23" s="120"/>
+    </row>
+    <row r="24" spans="1:16" ht="11.25" customHeight="1">
+      <c r="A24" s="252"/>
+      <c r="B24" s="313"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="569"/>
+      <c r="E24" s="569"/>
+      <c r="F24" s="569"/>
+      <c r="G24" s="569"/>
+      <c r="H24" s="850"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="307"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="109"/>
+      <c r="O24" s="275" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="25.5" customHeight="1">
+      <c r="A25" s="252"/>
+      <c r="B25" s="313"/>
+      <c r="C25" s="179" t="s">
+        <v>547</v>
+      </c>
+      <c r="D25" s="285" t="s">
+        <v>864</v>
+      </c>
+      <c r="E25" s="573" t="s">
+        <v>185</v>
+      </c>
+      <c r="F25" s="285" t="s">
+        <v>863</v>
+      </c>
+      <c r="G25" s="285" t="s">
+        <v>862</v>
+      </c>
+      <c r="H25" s="342" t="s">
+        <v>790</v>
+      </c>
+      <c r="K25" s="316" t="s">
+        <v>182</v>
+      </c>
+      <c r="M25" s="110"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="276"/>
+    </row>
+    <row r="26" spans="1:16" ht="29.25" customHeight="1">
+      <c r="A26" s="252"/>
+      <c r="B26" s="313"/>
+      <c r="C26" s="855" t="s">
+        <v>861</v>
+      </c>
+      <c r="D26" s="286"/>
+      <c r="E26" s="574"/>
+      <c r="F26" s="286"/>
+      <c r="G26" s="286"/>
+      <c r="H26" s="343"/>
+      <c r="K26" s="317"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="109"/>
+      <c r="O26" s="276"/>
+    </row>
+    <row r="27" spans="1:16" ht="29.25" customHeight="1">
+      <c r="A27" s="252"/>
+      <c r="B27" s="313"/>
+      <c r="C27" s="855"/>
+      <c r="D27" s="286"/>
+      <c r="E27" s="574"/>
+      <c r="F27" s="286"/>
+      <c r="G27" s="286"/>
+      <c r="H27" s="343"/>
+      <c r="K27" s="317"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="119"/>
+    </row>
+    <row r="28" spans="1:16" ht="29.25" customHeight="1">
+      <c r="A28" s="252"/>
+      <c r="B28" s="313"/>
+      <c r="C28" s="855"/>
+      <c r="D28" s="286"/>
+      <c r="E28" s="574"/>
+      <c r="F28" s="328"/>
+      <c r="G28" s="328"/>
+      <c r="H28" s="344"/>
+      <c r="K28" s="318"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="319" t="s">
+        <v>181</v>
+      </c>
+      <c r="N28" s="319" t="s">
+        <v>180</v>
+      </c>
+      <c r="O28" s="275" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A29" s="252"/>
+      <c r="B29" s="232" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="342" t="s">
+        <v>310</v>
+      </c>
+      <c r="D29" s="342" t="s">
+        <v>860</v>
+      </c>
+      <c r="E29" s="349" t="s">
+        <v>859</v>
+      </c>
+      <c r="F29" s="342" t="s">
+        <v>748</v>
+      </c>
+      <c r="G29" s="305" t="s">
+        <v>858</v>
+      </c>
+      <c r="H29" s="571" t="s">
+        <v>857</v>
+      </c>
+      <c r="K29" s="118"/>
+      <c r="L29" s="572"/>
+      <c r="M29" s="320"/>
+      <c r="N29" s="320"/>
+      <c r="O29" s="276"/>
+    </row>
+    <row r="30" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A30" s="252"/>
+      <c r="B30" s="232"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="350"/>
+      <c r="F30" s="343"/>
+      <c r="G30" s="306"/>
+      <c r="H30" s="331"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="572"/>
+      <c r="M30" s="320"/>
+      <c r="N30" s="320"/>
+      <c r="O30" s="276"/>
+    </row>
+    <row r="31" spans="1:16" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A31" s="252"/>
+      <c r="B31" s="232"/>
+      <c r="C31" s="343"/>
+      <c r="D31" s="343"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="343"/>
+      <c r="G31" s="306"/>
+      <c r="H31" s="331"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="572"/>
+      <c r="M31" s="321"/>
+      <c r="N31" s="321"/>
+      <c r="O31" s="277"/>
+    </row>
+    <row r="32" spans="1:16" ht="26.25" customHeight="1">
+      <c r="A32" s="252"/>
+      <c r="B32" s="232"/>
+      <c r="C32" s="344"/>
+      <c r="D32" s="344"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="344"/>
+      <c r="G32" s="307"/>
+      <c r="H32" s="331"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="114"/>
+      <c r="N32" s="114"/>
+    </row>
+    <row r="33" spans="1:15" ht="21.75" customHeight="1">
+      <c r="A33" s="252"/>
+      <c r="B33" s="232"/>
+      <c r="C33" s="348" t="s">
+        <v>744</v>
+      </c>
+      <c r="D33" s="348" t="s">
+        <v>856</v>
+      </c>
+      <c r="E33" s="350"/>
+      <c r="F33" s="851" t="s">
+        <v>743</v>
+      </c>
+      <c r="G33" s="348" t="s">
+        <v>855</v>
+      </c>
+      <c r="H33" s="331"/>
+      <c r="K33" s="333" t="s">
+        <v>168</v>
+      </c>
+      <c r="L33" s="116" t="s">
+        <v>168</v>
+      </c>
+      <c r="M33" s="114"/>
+      <c r="N33" s="114"/>
+    </row>
+    <row r="34" spans="1:15" ht="21.75" customHeight="1">
+      <c r="A34" s="252"/>
+      <c r="B34" s="232"/>
+      <c r="C34" s="348"/>
+      <c r="D34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="851"/>
+      <c r="G34" s="348"/>
+      <c r="H34" s="331"/>
+      <c r="K34" s="334"/>
+      <c r="L34" s="115"/>
+      <c r="M34" s="114"/>
+      <c r="N34" s="114"/>
+    </row>
+    <row r="35" spans="1:15" ht="21.75" customHeight="1">
+      <c r="A35" s="252"/>
+      <c r="B35" s="232"/>
+      <c r="C35" s="348"/>
+      <c r="D35" s="348"/>
+      <c r="E35" s="350"/>
+      <c r="F35" s="851"/>
+      <c r="G35" s="348"/>
+      <c r="H35" s="331"/>
+      <c r="K35" s="334"/>
+      <c r="L35" s="115"/>
+      <c r="M35" s="114"/>
+      <c r="N35" s="114"/>
+    </row>
+    <row r="36" spans="1:15" ht="21.75" customHeight="1">
+      <c r="A36" s="252"/>
+      <c r="B36" s="232"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="350"/>
+      <c r="F36" s="851"/>
+      <c r="G36" s="348"/>
+      <c r="H36" s="331"/>
+      <c r="K36" s="335"/>
+      <c r="L36" s="113"/>
+      <c r="M36" s="110"/>
+      <c r="N36" s="109"/>
+    </row>
+    <row r="37" spans="1:15" ht="26.25" customHeight="1">
+      <c r="A37" s="252"/>
+      <c r="B37" s="232"/>
+      <c r="C37" s="570" t="s">
+        <v>854</v>
+      </c>
+      <c r="D37" s="570" t="s">
+        <v>853</v>
+      </c>
+      <c r="E37" s="350"/>
+      <c r="F37" s="570" t="s">
+        <v>852</v>
+      </c>
+      <c r="G37" s="570" t="s">
+        <v>851</v>
+      </c>
+      <c r="H37" s="331"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="110"/>
+      <c r="N37" s="109"/>
+    </row>
+    <row r="38" spans="1:15" ht="26.25" customHeight="1">
+      <c r="A38" s="252"/>
+      <c r="B38" s="232"/>
+      <c r="C38" s="570"/>
+      <c r="D38" s="570"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="570"/>
+      <c r="G38" s="570"/>
+      <c r="H38" s="331"/>
+      <c r="K38" s="322" t="s">
+        <v>163</v>
+      </c>
+      <c r="L38" s="272" t="s">
+        <v>162</v>
+      </c>
+      <c r="M38" s="322" t="s">
+        <v>161</v>
+      </c>
+      <c r="N38" s="322" t="s">
+        <v>160</v>
+      </c>
+      <c r="O38" s="322" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="26.25" customHeight="1">
+      <c r="A39" s="252"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="570"/>
+      <c r="D39" s="570"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="570"/>
+      <c r="G39" s="570"/>
+      <c r="H39" s="331"/>
+      <c r="K39" s="323"/>
+      <c r="L39" s="273"/>
+      <c r="M39" s="323"/>
+      <c r="N39" s="323"/>
+      <c r="O39" s="323"/>
+    </row>
+    <row r="40" spans="1:15" ht="26.25" customHeight="1">
+      <c r="A40" s="252"/>
+      <c r="B40" s="232"/>
+      <c r="C40" s="570"/>
+      <c r="D40" s="570"/>
+      <c r="E40" s="351"/>
+      <c r="F40" s="570"/>
+      <c r="G40" s="570"/>
+      <c r="H40" s="332"/>
+      <c r="K40" s="323"/>
+      <c r="L40" s="273"/>
+      <c r="M40" s="323"/>
+      <c r="N40" s="323"/>
+      <c r="O40" s="323"/>
+    </row>
+    <row r="41" spans="1:15" ht="24" customHeight="1">
+      <c r="A41" s="251"/>
+      <c r="B41" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="329" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="254"/>
+      <c r="E41" s="254"/>
+      <c r="F41" s="254"/>
+      <c r="G41" s="254"/>
+      <c r="H41" s="330"/>
+      <c r="K41" s="324"/>
+      <c r="L41" s="274"/>
+      <c r="M41" s="324"/>
+      <c r="N41" s="324"/>
+      <c r="O41" s="324"/>
+    </row>
+    <row r="42" spans="1:15" ht="24" customHeight="1">
+      <c r="A42" s="300"/>
+      <c r="B42" s="106" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="365" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="366"/>
+      <c r="E42" s="366"/>
+      <c r="F42" s="366"/>
+      <c r="G42" s="366"/>
+      <c r="H42" s="367"/>
+    </row>
+    <row r="43" spans="1:15" ht="20.25" customHeight="1">
+      <c r="A43" s="358" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="359"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
+      <c r="G43" s="360"/>
+      <c r="H43" s="361"/>
+      <c r="K43" s="362" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="18">
+      <c r="A44" s="352" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="353"/>
+      <c r="C44" s="353"/>
+      <c r="D44" s="353"/>
+      <c r="E44" s="353"/>
+      <c r="F44" s="353"/>
+      <c r="G44" s="353"/>
+      <c r="H44" s="354"/>
+      <c r="K44" s="363"/>
+    </row>
+    <row r="45" spans="1:15" ht="18">
+      <c r="A45" s="352" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="353"/>
+      <c r="C45" s="353"/>
+      <c r="D45" s="353"/>
+      <c r="E45" s="353"/>
+      <c r="F45" s="353"/>
+      <c r="G45" s="353"/>
+      <c r="H45" s="354"/>
+      <c r="K45" s="363"/>
+    </row>
+    <row r="46" spans="1:15" ht="18">
+      <c r="A46" s="352" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="353"/>
+      <c r="C46" s="353"/>
+      <c r="D46" s="353"/>
+      <c r="E46" s="353"/>
+      <c r="F46" s="353"/>
+      <c r="G46" s="353"/>
+      <c r="H46" s="354"/>
+      <c r="K46" s="364"/>
+    </row>
+    <row r="47" spans="1:15" ht="18">
+      <c r="A47" s="352" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="353"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
+      <c r="G47" s="353"/>
+      <c r="H47" s="354"/>
+    </row>
+    <row r="48" spans="1:15" ht="18">
+      <c r="A48" s="352" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="353"/>
+      <c r="C48" s="353"/>
+      <c r="D48" s="353"/>
+      <c r="E48" s="353"/>
+      <c r="F48" s="353"/>
+      <c r="G48" s="353"/>
+      <c r="H48" s="354"/>
+    </row>
+    <row r="49" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A49" s="355"/>
+      <c r="B49" s="356"/>
+      <c r="C49" s="356"/>
+      <c r="D49" s="356"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
+      <c r="G49" s="356"/>
+      <c r="H49" s="357"/>
+    </row>
+    <row r="50" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A50" s="105"/>
+      <c r="H50" s="104"/>
+    </row>
+    <row r="51" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A51" s="105"/>
+      <c r="H51" s="104"/>
+    </row>
+    <row r="52" spans="1:11" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A52" s="103"/>
+      <c r="B52" s="102"/>
+      <c r="C52" s="101"/>
+      <c r="D52" s="101"/>
+      <c r="E52" s="101"/>
+      <c r="F52" s="101"/>
+      <c r="G52" s="101"/>
+      <c r="H52" s="100"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="K56" s="49"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="K60" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="91">
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="G25:G28"/>
+    <mergeCell ref="H25:H28"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="E29:E40"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="K43:K46"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="K38:K41"/>
+    <mergeCell ref="B29:B40"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="M38:M41"/>
+    <mergeCell ref="N38:N41"/>
+    <mergeCell ref="O38:O41"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="D37:D40"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="M28:M31"/>
+    <mergeCell ref="N28:N31"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="O28:O31"/>
+    <mergeCell ref="H29:H40"/>
+    <mergeCell ref="L29:L31"/>
+    <mergeCell ref="K33:K36"/>
+    <mergeCell ref="L38:L41"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="H12:H19"/>
+    <mergeCell ref="N16:N19"/>
+    <mergeCell ref="O16:O19"/>
+    <mergeCell ref="P16:P19"/>
+    <mergeCell ref="A20:A42"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="L21:L24"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="L12:L15"/>
+    <mergeCell ref="N12:N15"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="F16:F19"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="K16:K19"/>
+    <mergeCell ref="M16:M19"/>
+    <mergeCell ref="B10:B19"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:A19"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C9:H9"/>
+  </mergeCells>
+  <phoneticPr fontId="146" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.6692913385826772" bottom="0.39370078740157483" header="0.11811023622047245" footer="0"/>
+  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="8" max="16383" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05319774-EC11-7A46-9C40-BF13D5013B84}">
   <dimension ref="A1:P61"/>
